--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T15:07:43+00:00</t>
+    <t>2023-10-23T11:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:38:46+00:00</t>
+    <t>2023-11-06T10:27:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:27:25+00:00</t>
+    <t>2023-11-06T10:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:34:42+00:00</t>
+    <t>2023-11-06T13:10:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:10:33+00:00</t>
+    <t>2023-11-06T13:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:11:32+00:00</t>
+    <t>2023-11-06T13:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:14+00:00</t>
+    <t>2023-11-06T13:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-specialty.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-specialty</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:47+00:00</t>
+    <t>2023-11-08T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
